--- a/Team-Data/2012-13/12-13-2012-13.xlsx
+++ b/Team-Data/2012-13/12-13-2012-13.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,58 +728,58 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E2" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F2" t="n">
         <v>6</v>
       </c>
       <c r="G2" t="n">
-        <v>0.7</v>
+        <v>0.6840000000000001</v>
       </c>
       <c r="H2" t="n">
         <v>48.3</v>
       </c>
       <c r="I2" t="n">
-        <v>37.5</v>
+        <v>37.2</v>
       </c>
       <c r="J2" t="n">
-        <v>81.5</v>
+        <v>81.8</v>
       </c>
       <c r="K2" t="n">
-        <v>0.46</v>
+        <v>0.454</v>
       </c>
       <c r="L2" t="n">
-        <v>8.6</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="M2" t="n">
-        <v>23</v>
+        <v>22.7</v>
       </c>
       <c r="N2" t="n">
-        <v>0.374</v>
+        <v>0.367</v>
       </c>
       <c r="O2" t="n">
         <v>13.7</v>
       </c>
       <c r="P2" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.698</v>
+        <v>0.707</v>
       </c>
       <c r="R2" t="n">
-        <v>10.3</v>
+        <v>10.5</v>
       </c>
       <c r="S2" t="n">
-        <v>30</v>
+        <v>29.7</v>
       </c>
       <c r="T2" t="n">
-        <v>40.3</v>
+        <v>40.2</v>
       </c>
       <c r="U2" t="n">
-        <v>22.8</v>
+        <v>22.5</v>
       </c>
       <c r="V2" t="n">
         <v>14.9</v>
@@ -721,100 +788,100 @@
         <v>9.300000000000001</v>
       </c>
       <c r="X2" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Y2" t="n">
-        <v>4.3</v>
+        <v>4.5</v>
       </c>
       <c r="Z2" t="n">
-        <v>17.7</v>
+        <v>17.8</v>
       </c>
       <c r="AA2" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="AB2" t="n">
-        <v>97.2</v>
+        <v>96.3</v>
       </c>
       <c r="AC2" t="n">
-        <v>4.1</v>
+        <v>3.1</v>
       </c>
       <c r="AD2" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AE2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AF2" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AH2" t="n">
         <v>20</v>
       </c>
       <c r="AI2" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AJ2" t="n">
         <v>19</v>
       </c>
       <c r="AK2" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="AL2" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AM2" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN2" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AO2" t="n">
         <v>29</v>
       </c>
       <c r="AP2" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AQ2" t="n">
         <v>28</v>
       </c>
       <c r="AR2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AT2" t="n">
         <v>27</v>
       </c>
       <c r="AU2" t="n">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="AV2" t="n">
         <v>13</v>
       </c>
       <c r="AW2" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AX2" t="n">
         <v>22</v>
       </c>
       <c r="AY2" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AZ2" t="n">
         <v>1</v>
       </c>
       <c r="BA2" t="n">
+        <v>18</v>
+      </c>
+      <c r="BB2" t="n">
         <v>17</v>
       </c>
-      <c r="BB2" t="n">
-        <v>15</v>
-      </c>
       <c r="BC2" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>12-13-2012-13</t>
+          <t>2012-12-13</t>
         </is>
       </c>
     </row>
@@ -921,7 +988,7 @@
         <v>0.8</v>
       </c>
       <c r="AD3" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE3" t="n">
         <v>10</v>
@@ -936,7 +1003,7 @@
         <v>1</v>
       </c>
       <c r="AI3" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ3" t="n">
         <v>25</v>
@@ -951,7 +1018,7 @@
         <v>29</v>
       </c>
       <c r="AN3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AO3" t="n">
         <v>10</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>12-13-2012-13</t>
+          <t>2012-12-13</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>2.3</v>
       </c>
       <c r="AD4" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE4" t="n">
         <v>10</v>
@@ -1133,7 +1200,7 @@
         <v>7</v>
       </c>
       <c r="AN4" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AO4" t="n">
         <v>14</v>
@@ -1151,7 +1218,7 @@
         <v>26</v>
       </c>
       <c r="AT4" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AU4" t="n">
         <v>15</v>
@@ -1175,10 +1242,10 @@
         <v>5</v>
       </c>
       <c r="BB4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BC4" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>12-13-2012-13</t>
+          <t>2012-12-13</t>
         </is>
       </c>
     </row>
@@ -1207,25 +1274,25 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E5" t="n">
         <v>7</v>
       </c>
       <c r="F5" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G5" t="n">
-        <v>0.318</v>
+        <v>0.333</v>
       </c>
       <c r="H5" t="n">
-        <v>48.9</v>
+        <v>49</v>
       </c>
       <c r="I5" t="n">
-        <v>35</v>
+        <v>35.1</v>
       </c>
       <c r="J5" t="n">
-        <v>83.40000000000001</v>
+        <v>83.59999999999999</v>
       </c>
       <c r="K5" t="n">
         <v>0.42</v>
@@ -1234,67 +1301,67 @@
         <v>6.5</v>
       </c>
       <c r="M5" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="N5" t="n">
-        <v>0.34</v>
+        <v>0.343</v>
       </c>
       <c r="O5" t="n">
-        <v>19.3</v>
+        <v>19.5</v>
       </c>
       <c r="P5" t="n">
-        <v>25.2</v>
+        <v>25.4</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.767</v>
+        <v>0.766</v>
       </c>
       <c r="R5" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S5" t="n">
-        <v>30</v>
+        <v>30.3</v>
       </c>
       <c r="T5" t="n">
-        <v>41.4</v>
+        <v>41.9</v>
       </c>
       <c r="U5" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="V5" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W5" t="n">
-        <v>7.9</v>
+        <v>8</v>
       </c>
       <c r="X5" t="n">
-        <v>6.6</v>
+        <v>6.9</v>
       </c>
       <c r="Y5" t="n">
-        <v>8.1</v>
+        <v>8.4</v>
       </c>
       <c r="Z5" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.5</v>
+        <v>20.8</v>
       </c>
       <c r="AB5" t="n">
-        <v>95.90000000000001</v>
+        <v>96.09999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>-7.9</v>
+        <v>-7.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AE5" t="n">
         <v>24</v>
       </c>
       <c r="AF5" t="n">
+        <v>23</v>
+      </c>
+      <c r="AG5" t="n">
         <v>24</v>
-      </c>
-      <c r="AG5" t="n">
-        <v>25</v>
       </c>
       <c r="AH5" t="n">
         <v>5</v>
@@ -1312,16 +1379,16 @@
         <v>19</v>
       </c>
       <c r="AM5" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AN5" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AO5" t="n">
         <v>5</v>
       </c>
       <c r="AP5" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ5" t="n">
         <v>12</v>
@@ -1330,10 +1397,10 @@
         <v>16</v>
       </c>
       <c r="AS5" t="n">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="AT5" t="n">
-        <v>21</v>
+        <v>16</v>
       </c>
       <c r="AU5" t="n">
         <v>28</v>
@@ -1342,7 +1409,7 @@
         <v>8</v>
       </c>
       <c r="AW5" t="n">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="AX5" t="n">
         <v>5</v>
@@ -1354,13 +1421,13 @@
         <v>12</v>
       </c>
       <c r="BA5" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="BB5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BC5" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BD5" t="n">
         <v>10</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>12-13-2012-13</t>
+          <t>2012-12-13</t>
         </is>
       </c>
     </row>
@@ -1467,7 +1534,7 @@
         <v>2.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE6" t="n">
         <v>10</v>
@@ -1542,7 +1609,7 @@
         <v>24</v>
       </c>
       <c r="BC6" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="BD6" t="n">
         <v>10</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>12-13-2012-13</t>
+          <t>2012-12-13</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>-6</v>
       </c>
       <c r="AD7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE7" t="n">
         <v>27</v>
@@ -1676,7 +1743,7 @@
         <v>7</v>
       </c>
       <c r="AM7" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN7" t="n">
         <v>16</v>
@@ -1694,7 +1761,7 @@
         <v>2</v>
       </c>
       <c r="AS7" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AT7" t="n">
         <v>13</v>
@@ -1706,7 +1773,7 @@
         <v>25</v>
       </c>
       <c r="AW7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AX7" t="n">
         <v>30</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>12-13-2012-13</t>
+          <t>2012-12-13</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>-0.5</v>
       </c>
       <c r="AD8" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE8" t="n">
         <v>14</v>
@@ -1843,19 +1910,19 @@
         <v>16</v>
       </c>
       <c r="AH8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AI8" t="n">
         <v>5</v>
       </c>
       <c r="AJ8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AK8" t="n">
         <v>9</v>
       </c>
       <c r="AL8" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AM8" t="n">
         <v>11</v>
@@ -1864,7 +1931,7 @@
         <v>5</v>
       </c>
       <c r="AO8" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AP8" t="n">
         <v>20</v>
@@ -1879,7 +1946,7 @@
         <v>7</v>
       </c>
       <c r="AT8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU8" t="n">
         <v>10</v>
@@ -1888,13 +1955,13 @@
         <v>23</v>
       </c>
       <c r="AW8" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AX8" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AY8" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ8" t="n">
         <v>27</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>12-13-2012-13</t>
+          <t>2012-12-13</t>
         </is>
       </c>
     </row>
@@ -2013,7 +2080,7 @@
         <v>-0.1</v>
       </c>
       <c r="AD9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE9" t="n">
         <v>14</v>
@@ -2070,7 +2137,7 @@
         <v>28</v>
       </c>
       <c r="AW9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX9" t="n">
         <v>6</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>12-13-2012-13</t>
+          <t>2012-12-13</t>
         </is>
       </c>
     </row>
@@ -2213,7 +2280,7 @@
         <v>26</v>
       </c>
       <c r="AJ10" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AK10" t="n">
         <v>17</v>
@@ -2225,13 +2292,13 @@
         <v>27</v>
       </c>
       <c r="AN10" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO10" t="n">
         <v>9</v>
       </c>
       <c r="AP10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ10" t="n">
         <v>24</v>
@@ -2240,13 +2307,13 @@
         <v>18</v>
       </c>
       <c r="AS10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AT10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU10" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AV10" t="n">
         <v>17</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>12-13-2012-13</t>
+          <t>2012-12-13</t>
         </is>
       </c>
     </row>
@@ -2377,7 +2444,7 @@
         <v>1</v>
       </c>
       <c r="AD11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE11" t="n">
         <v>5</v>
@@ -2413,7 +2480,7 @@
         <v>13</v>
       </c>
       <c r="AP11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>12-13-2012-13</t>
+          <t>2012-12-13</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>-0.6</v>
       </c>
       <c r="AD12" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE12" t="n">
         <v>18</v>
@@ -2574,7 +2641,7 @@
         <v>8</v>
       </c>
       <c r="AI12" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AJ12" t="n">
         <v>4</v>
@@ -2610,7 +2677,7 @@
         <v>6</v>
       </c>
       <c r="AU12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV12" t="n">
         <v>30</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>12-13-2012-13</t>
+          <t>2012-12-13</t>
         </is>
       </c>
     </row>
@@ -2741,7 +2808,7 @@
         <v>-0.3</v>
       </c>
       <c r="AD13" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE13" t="n">
         <v>14</v>
@@ -2777,7 +2844,7 @@
         <v>19</v>
       </c>
       <c r="AP13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AQ13" t="n">
         <v>21</v>
@@ -2786,7 +2853,7 @@
         <v>6</v>
       </c>
       <c r="AS13" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AT13" t="n">
         <v>1</v>
@@ -2810,7 +2877,7 @@
         <v>7</v>
       </c>
       <c r="BA13" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BB13" t="n">
         <v>29</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>12-13-2012-13</t>
+          <t>2012-12-13</t>
         </is>
       </c>
     </row>
@@ -2923,19 +2990,19 @@
         <v>7.6</v>
       </c>
       <c r="AD14" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG14" t="n">
         <v>5</v>
       </c>
       <c r="AH14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AI14" t="n">
         <v>4</v>
@@ -2974,7 +3041,7 @@
         <v>22</v>
       </c>
       <c r="AU14" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV14" t="n">
         <v>10</v>
@@ -2986,7 +3053,7 @@
         <v>7</v>
       </c>
       <c r="AY14" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AZ14" t="n">
         <v>24</v>
@@ -2998,7 +3065,7 @@
         <v>6</v>
       </c>
       <c r="BC14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BD14" t="n">
         <v>10</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>12-13-2012-13</t>
+          <t>2012-12-13</t>
         </is>
       </c>
     </row>
@@ -3027,16 +3094,16 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E15" t="n">
         <v>9</v>
       </c>
       <c r="F15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G15" t="n">
-        <v>0.391</v>
+        <v>0.409</v>
       </c>
       <c r="H15" t="n">
         <v>48</v>
@@ -3045,73 +3112,73 @@
         <v>35.9</v>
       </c>
       <c r="J15" t="n">
-        <v>79.2</v>
+        <v>79</v>
       </c>
       <c r="K15" t="n">
-        <v>0.453</v>
+        <v>0.455</v>
       </c>
       <c r="L15" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="M15" t="n">
-        <v>23.9</v>
+        <v>23.3</v>
       </c>
       <c r="N15" t="n">
-        <v>0.377</v>
+        <v>0.381</v>
       </c>
       <c r="O15" t="n">
-        <v>21</v>
+        <v>20.8</v>
       </c>
       <c r="P15" t="n">
-        <v>30.7</v>
+        <v>30.8</v>
       </c>
       <c r="Q15" t="n">
-        <v>0.6830000000000001</v>
+        <v>0.675</v>
       </c>
       <c r="R15" t="n">
-        <v>13.1</v>
+        <v>13.2</v>
       </c>
       <c r="S15" t="n">
-        <v>33</v>
+        <v>33.1</v>
       </c>
       <c r="T15" t="n">
-        <v>46.2</v>
+        <v>46.3</v>
       </c>
       <c r="U15" t="n">
-        <v>20.3</v>
+        <v>20.7</v>
       </c>
       <c r="V15" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="W15" t="n">
-        <v>7.7</v>
+        <v>7.8</v>
       </c>
       <c r="X15" t="n">
         <v>5.6</v>
       </c>
       <c r="Y15" t="n">
-        <v>4.7</v>
+        <v>4.8</v>
       </c>
       <c r="Z15" t="n">
         <v>20</v>
       </c>
       <c r="AA15" t="n">
-        <v>24.3</v>
+        <v>24.5</v>
       </c>
       <c r="AB15" t="n">
-        <v>101.7</v>
+        <v>101.5</v>
       </c>
       <c r="AC15" t="n">
-        <v>2.2</v>
+        <v>2.7</v>
       </c>
       <c r="AD15" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AE15" t="n">
+        <v>20</v>
+      </c>
+      <c r="AF15" t="n">
         <v>21</v>
-      </c>
-      <c r="AF15" t="n">
-        <v>22</v>
       </c>
       <c r="AG15" t="n">
         <v>21</v>
@@ -3123,10 +3190,10 @@
         <v>20</v>
       </c>
       <c r="AJ15" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AK15" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="AL15" t="n">
         <v>3</v>
@@ -3156,7 +3223,7 @@
         <v>2</v>
       </c>
       <c r="AU15" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AV15" t="n">
         <v>29</v>
@@ -3165,7 +3232,7 @@
         <v>21</v>
       </c>
       <c r="AX15" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AY15" t="n">
         <v>11</v>
@@ -3180,7 +3247,7 @@
         <v>7</v>
       </c>
       <c r="BC15" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="BD15" t="n">
         <v>10</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>12-13-2012-13</t>
+          <t>2012-12-13</t>
         </is>
       </c>
     </row>
@@ -3287,7 +3354,7 @@
         <v>6.5</v>
       </c>
       <c r="AD16" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE16" t="n">
         <v>6</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>12-13-2012-13</t>
+          <t>2012-12-13</t>
         </is>
       </c>
     </row>
@@ -3475,13 +3542,13 @@
         <v>6</v>
       </c>
       <c r="AF17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AG17" t="n">
         <v>6</v>
       </c>
       <c r="AH17" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI17" t="n">
         <v>3</v>
@@ -3493,7 +3560,7 @@
         <v>1</v>
       </c>
       <c r="AL17" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AM17" t="n">
         <v>12</v>
@@ -3505,10 +3572,10 @@
         <v>15</v>
       </c>
       <c r="AP17" t="n">
+        <v>16</v>
+      </c>
+      <c r="AQ17" t="n">
         <v>15</v>
-      </c>
-      <c r="AQ17" t="n">
-        <v>16</v>
       </c>
       <c r="AR17" t="n">
         <v>29</v>
@@ -3526,7 +3593,7 @@
         <v>6</v>
       </c>
       <c r="AW17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX17" t="n">
         <v>24</v>
@@ -3538,13 +3605,13 @@
         <v>8</v>
       </c>
       <c r="BA17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BB17" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="BC17" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>12-13-2012-13</t>
+          <t>2012-12-13</t>
         </is>
       </c>
     </row>
@@ -3663,7 +3730,7 @@
         <v>13</v>
       </c>
       <c r="AH18" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AI18" t="n">
         <v>7</v>
@@ -3702,7 +3769,7 @@
         <v>11</v>
       </c>
       <c r="AU18" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV18" t="n">
         <v>4</v>
@@ -3723,7 +3790,7 @@
         <v>26</v>
       </c>
       <c r="BB18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC18" t="n">
         <v>16</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>12-13-2012-13</t>
+          <t>2012-12-13</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>1.4</v>
       </c>
       <c r="AD19" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE19" t="n">
         <v>18</v>
@@ -3860,7 +3927,7 @@
         <v>26</v>
       </c>
       <c r="AM19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AN19" t="n">
         <v>30</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>12-13-2012-13</t>
+          <t>2012-12-13</t>
         </is>
       </c>
     </row>
@@ -4015,7 +4082,7 @@
         <v>-6.2</v>
       </c>
       <c r="AD20" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE20" t="n">
         <v>27</v>
@@ -4033,7 +4100,7 @@
         <v>27</v>
       </c>
       <c r="AJ20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK20" t="n">
         <v>21</v>
@@ -4051,7 +4118,7 @@
         <v>26</v>
       </c>
       <c r="AP20" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AQ20" t="n">
         <v>7</v>
@@ -4060,7 +4127,7 @@
         <v>21</v>
       </c>
       <c r="AS20" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT20" t="n">
         <v>23</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>12-13-2012-13</t>
+          <t>2012-12-13</t>
         </is>
       </c>
     </row>
@@ -4119,85 +4186,85 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E21" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F21" t="n">
         <v>5</v>
       </c>
       <c r="G21" t="n">
-        <v>0.773</v>
+        <v>0.762</v>
       </c>
       <c r="H21" t="n">
         <v>48.2</v>
       </c>
       <c r="I21" t="n">
-        <v>37.4</v>
+        <v>37.2</v>
       </c>
       <c r="J21" t="n">
-        <v>83</v>
+        <v>83.09999999999999</v>
       </c>
       <c r="K21" t="n">
-        <v>0.451</v>
+        <v>0.447</v>
       </c>
       <c r="L21" t="n">
         <v>12</v>
       </c>
       <c r="M21" t="n">
-        <v>29.1</v>
+        <v>29.3</v>
       </c>
       <c r="N21" t="n">
-        <v>0.412</v>
+        <v>0.409</v>
       </c>
       <c r="O21" t="n">
-        <v>16.4</v>
+        <v>16.2</v>
       </c>
       <c r="P21" t="n">
-        <v>21.6</v>
+        <v>21.2</v>
       </c>
       <c r="Q21" t="n">
-        <v>0.758</v>
+        <v>0.765</v>
       </c>
       <c r="R21" t="n">
-        <v>10.1</v>
+        <v>10.4</v>
       </c>
       <c r="S21" t="n">
         <v>29.3</v>
       </c>
       <c r="T21" t="n">
-        <v>39.4</v>
+        <v>39.7</v>
       </c>
       <c r="U21" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="V21" t="n">
-        <v>10.6</v>
+        <v>10.9</v>
       </c>
       <c r="W21" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="X21" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Y21" t="n">
         <v>4.2</v>
       </c>
       <c r="Z21" t="n">
-        <v>18.9</v>
+        <v>18.8</v>
       </c>
       <c r="AA21" t="n">
-        <v>19.5</v>
+        <v>19.4</v>
       </c>
       <c r="AB21" t="n">
-        <v>103.2</v>
+        <v>102.6</v>
       </c>
       <c r="AC21" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="AD21" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AE21" t="n">
         <v>3</v>
@@ -4206,16 +4273,16 @@
         <v>2</v>
       </c>
       <c r="AG21" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AH21" t="n">
-        <v>26</v>
+        <v>23</v>
       </c>
       <c r="AI21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AJ21" t="n">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="AK21" t="n">
         <v>12</v>
@@ -4236,13 +4303,13 @@
         <v>21</v>
       </c>
       <c r="AQ21" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR21" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AT21" t="n">
         <v>28</v>
@@ -4266,10 +4333,10 @@
         <v>4</v>
       </c>
       <c r="BA21" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB21" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="BC21" t="n">
         <v>4</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>12-13-2012-13</t>
+          <t>2012-12-13</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>9.300000000000001</v>
       </c>
       <c r="AD22" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE22" t="n">
         <v>1</v>
@@ -4394,7 +4461,7 @@
         <v>16</v>
       </c>
       <c r="AI22" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="AJ22" t="n">
         <v>30</v>
@@ -4451,7 +4518,7 @@
         <v>4</v>
       </c>
       <c r="BB22" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BC22" t="n">
         <v>1</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>12-13-2012-13</t>
+          <t>2012-12-13</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>-3.5</v>
       </c>
       <c r="AD23" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE23" t="n">
         <v>22</v>
@@ -4579,7 +4646,7 @@
         <v>15</v>
       </c>
       <c r="AJ23" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AK23" t="n">
         <v>18</v>
@@ -4603,19 +4670,19 @@
         <v>6</v>
       </c>
       <c r="AR23" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AS23" t="n">
         <v>5</v>
       </c>
       <c r="AT23" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AU23" t="n">
         <v>12</v>
       </c>
       <c r="AV23" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AW23" t="n">
         <v>30</v>
@@ -4636,7 +4703,7 @@
         <v>27</v>
       </c>
       <c r="BC23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BD23" t="n">
         <v>10</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>12-13-2012-13</t>
+          <t>2012-12-13</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>-2</v>
       </c>
       <c r="AD24" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AE24" t="n">
         <v>10</v>
@@ -4788,10 +4855,10 @@
         <v>20</v>
       </c>
       <c r="AS24" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT24" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AU24" t="n">
         <v>17</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>12-13-2012-13</t>
+          <t>2012-12-13</t>
         </is>
       </c>
     </row>
@@ -4925,13 +4992,13 @@
         <v>-5</v>
       </c>
       <c r="AD25" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE25" t="n">
         <v>22</v>
       </c>
       <c r="AF25" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AG25" t="n">
         <v>23</v>
@@ -4994,10 +5061,10 @@
         <v>21</v>
       </c>
       <c r="BA25" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC25" t="n">
         <v>24</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>12-13-2012-13</t>
+          <t>2012-12-13</t>
         </is>
       </c>
     </row>
@@ -5029,52 +5096,52 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E26" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="F26" t="n">
         <v>12</v>
       </c>
       <c r="G26" t="n">
-        <v>0.455</v>
+        <v>0.429</v>
       </c>
       <c r="H26" t="n">
-        <v>49.1</v>
+        <v>49.2</v>
       </c>
       <c r="I26" t="n">
-        <v>36.2</v>
+        <v>36</v>
       </c>
       <c r="J26" t="n">
-        <v>83.3</v>
+        <v>83</v>
       </c>
       <c r="K26" t="n">
-        <v>0.434</v>
+        <v>0.433</v>
       </c>
       <c r="L26" t="n">
         <v>7.9</v>
       </c>
       <c r="M26" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="N26" t="n">
-        <v>0.341</v>
+        <v>0.346</v>
       </c>
       <c r="O26" t="n">
-        <v>17</v>
+        <v>17.2</v>
       </c>
       <c r="P26" t="n">
-        <v>22.4</v>
+        <v>22.9</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.758</v>
+        <v>0.754</v>
       </c>
       <c r="R26" t="n">
-        <v>11.8</v>
+        <v>12</v>
       </c>
       <c r="S26" t="n">
-        <v>28.6</v>
+        <v>28.5</v>
       </c>
       <c r="T26" t="n">
         <v>40.4</v>
@@ -5086,31 +5153,31 @@
         <v>15</v>
       </c>
       <c r="W26" t="n">
-        <v>8.4</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="X26" t="n">
         <v>4.9</v>
       </c>
       <c r="Y26" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z26" t="n">
         <v>20.2</v>
       </c>
       <c r="AA26" t="n">
-        <v>19.8</v>
+        <v>20.2</v>
       </c>
       <c r="AB26" t="n">
-        <v>97.2</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC26" t="n">
-        <v>-3</v>
+        <v>-3.5</v>
       </c>
       <c r="AD26" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="AE26" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AF26" t="n">
         <v>19</v>
@@ -5119,13 +5186,13 @@
         <v>20</v>
       </c>
       <c r="AH26" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI26" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AJ26" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AK26" t="n">
         <v>22</v>
@@ -5140,19 +5207,19 @@
         <v>18</v>
       </c>
       <c r="AO26" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AP26" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AQ26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AR26" t="n">
         <v>12</v>
       </c>
       <c r="AS26" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AT26" t="n">
         <v>24</v>
@@ -5164,25 +5231,25 @@
         <v>14</v>
       </c>
       <c r="AW26" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AX26" t="n">
         <v>20</v>
       </c>
       <c r="AY26" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="AZ26" t="n">
         <v>15</v>
       </c>
       <c r="BA26" t="n">
-        <v>20</v>
+        <v>17</v>
       </c>
       <c r="BB26" t="n">
         <v>14</v>
       </c>
       <c r="BC26" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>12-13-2012-13</t>
+          <t>2012-12-13</t>
         </is>
       </c>
     </row>
@@ -5289,13 +5356,13 @@
         <v>-5.3</v>
       </c>
       <c r="AD27" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AE27" t="n">
         <v>24</v>
       </c>
       <c r="AF27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG27" t="n">
         <v>24</v>
@@ -5304,7 +5371,7 @@
         <v>14</v>
       </c>
       <c r="AI27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ27" t="n">
         <v>12</v>
@@ -5319,7 +5386,7 @@
         <v>22</v>
       </c>
       <c r="AN27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AO27" t="n">
         <v>23</v>
@@ -5334,10 +5401,10 @@
         <v>17</v>
       </c>
       <c r="AS27" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AT27" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AU27" t="n">
         <v>30</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>12-13-2012-13</t>
+          <t>2012-12-13</t>
         </is>
       </c>
     </row>
@@ -5393,94 +5460,94 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E28" t="n">
         <v>18</v>
       </c>
       <c r="F28" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G28" t="n">
-        <v>0.75</v>
+        <v>0.783</v>
       </c>
       <c r="H28" t="n">
-        <v>48.8</v>
+        <v>48.9</v>
       </c>
       <c r="I28" t="n">
-        <v>39.9</v>
+        <v>40.2</v>
       </c>
       <c r="J28" t="n">
-        <v>83</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K28" t="n">
-        <v>0.481</v>
+        <v>0.482</v>
       </c>
       <c r="L28" t="n">
-        <v>8.4</v>
+        <v>8.5</v>
       </c>
       <c r="M28" t="n">
-        <v>22.3</v>
+        <v>22.4</v>
       </c>
       <c r="N28" t="n">
-        <v>0.376</v>
+        <v>0.378</v>
       </c>
       <c r="O28" t="n">
         <v>16.6</v>
       </c>
       <c r="P28" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.787</v>
+        <v>0.79</v>
       </c>
       <c r="R28" t="n">
-        <v>9.199999999999999</v>
+        <v>9.300000000000001</v>
       </c>
       <c r="S28" t="n">
-        <v>33.7</v>
+        <v>33.8</v>
       </c>
       <c r="T28" t="n">
-        <v>42.9</v>
+        <v>43.1</v>
       </c>
       <c r="U28" t="n">
-        <v>25.3</v>
+        <v>25.4</v>
       </c>
       <c r="V28" t="n">
-        <v>15.5</v>
+        <v>15.3</v>
       </c>
       <c r="W28" t="n">
         <v>8.1</v>
       </c>
       <c r="X28" t="n">
-        <v>5.2</v>
+        <v>5.3</v>
       </c>
       <c r="Y28" t="n">
         <v>5.3</v>
       </c>
       <c r="Z28" t="n">
-        <v>17.7</v>
+        <v>18</v>
       </c>
       <c r="AA28" t="n">
         <v>19.1</v>
       </c>
       <c r="AB28" t="n">
-        <v>104.8</v>
+        <v>105.5</v>
       </c>
       <c r="AC28" t="n">
-        <v>7.5</v>
+        <v>8.1</v>
       </c>
       <c r="AD28" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE28" t="n">
         <v>1</v>
       </c>
       <c r="AF28" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AG28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH28" t="n">
         <v>7</v>
@@ -5489,19 +5556,19 @@
         <v>1</v>
       </c>
       <c r="AJ28" t="n">
-        <v>14</v>
+        <v>9</v>
       </c>
       <c r="AK28" t="n">
         <v>3</v>
       </c>
       <c r="AL28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AM28" t="n">
         <v>8</v>
       </c>
       <c r="AN28" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AO28" t="n">
         <v>20</v>
@@ -5516,16 +5583,16 @@
         <v>28</v>
       </c>
       <c r="AS28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AT28" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AU28" t="n">
         <v>1</v>
       </c>
       <c r="AV28" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AW28" t="n">
         <v>14</v>
@@ -5543,10 +5610,10 @@
         <v>27</v>
       </c>
       <c r="BB28" t="n">
+        <v>1</v>
+      </c>
+      <c r="BC28" t="n">
         <v>2</v>
-      </c>
-      <c r="BC28" t="n">
-        <v>3</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>12-13-2012-13</t>
+          <t>2012-12-13</t>
         </is>
       </c>
     </row>
@@ -5653,7 +5720,7 @@
         <v>-7.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE29" t="n">
         <v>29</v>
@@ -5671,7 +5738,7 @@
         <v>23</v>
       </c>
       <c r="AJ29" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AK29" t="n">
         <v>26</v>
@@ -5689,7 +5756,7 @@
         <v>11</v>
       </c>
       <c r="AP29" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AQ29" t="n">
         <v>8</v>
@@ -5704,7 +5771,7 @@
         <v>25</v>
       </c>
       <c r="AU29" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV29" t="n">
         <v>3</v>
@@ -5722,13 +5789,13 @@
         <v>30</v>
       </c>
       <c r="BA29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BB29" t="n">
         <v>20</v>
       </c>
       <c r="BC29" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>12-13-2012-13</t>
+          <t>2012-12-13</t>
         </is>
       </c>
     </row>
@@ -5835,10 +5902,10 @@
         <v>2</v>
       </c>
       <c r="AD30" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE30" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AF30" t="n">
         <v>14</v>
@@ -5853,7 +5920,7 @@
         <v>8</v>
       </c>
       <c r="AJ30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AK30" t="n">
         <v>11</v>
@@ -5865,7 +5932,7 @@
         <v>21</v>
       </c>
       <c r="AN30" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO30" t="n">
         <v>6</v>
@@ -5874,13 +5941,13 @@
         <v>8</v>
       </c>
       <c r="AQ30" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR30" t="n">
         <v>3</v>
       </c>
       <c r="AS30" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AT30" t="n">
         <v>8</v>
@@ -5904,7 +5971,7 @@
         <v>26</v>
       </c>
       <c r="BA30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB30" t="n">
         <v>8</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>12-13-2012-13</t>
+          <t>2012-12-13</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-6.6</v>
       </c>
       <c r="AD31" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AE31" t="n">
         <v>30</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>12-13-2012-13</t>
+          <t>2012-12-13</t>
         </is>
       </c>
     </row>
